--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V94"/>
+  <dimension ref="B1:V99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1072,19 +1072,34 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Number of Claims (optional)</t>
+        </is>
+      </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
           <t>Section</t>
@@ -1121,6 +1136,11 @@
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="V12" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1144,19 +1164,34 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Number of Claims (optional)</t>
+        </is>
+      </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
           <t>Section</t>
@@ -1193,6 +1228,11 @@
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="V13" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1527,7 +1567,7 @@
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1539,457 +1579,345 @@
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="2" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="8" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="3" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="8" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" s="10" t="n">
+    <row r="70">
+      <c r="B70" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="B67" s="10" t="n">
+    <row r="71">
+      <c r="B71" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="10" t="n">
+    <row r="72">
+      <c r="B72" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="2" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="3" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C74" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="8" t="inlineStr">
-        <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="D76" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>01.Incurred Losses@{Y}</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
@@ -2002,179 +1930,379 @@
       </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>01.Premium@{N}</t>
+        </is>
+      </c>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>a full-year N in History is an estimate, not an actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>SUM(03.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>large losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="8" t="inlineStr">
+        <is>
           <t>R-09</t>
         </is>
       </c>
-      <c r="C79" s="11" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr">
+      <c r="E83" s="11" t="inlineStr">
         <is>
           <t>03.Year basis</t>
         </is>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F83" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G83" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H83" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>history and large losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="8" t="inlineStr">
         <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>history and cat losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="8" t="inlineStr">
+        <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C89" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="12" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>Transpose_i</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="12" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="12" t="inlineStr">
         <is>
+          <t>Info_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" s="12" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="8" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2197,10 +2325,12 @@
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -2260,10 +2390,17 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Occurrence year from = Event Date</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Claim no.</t>
+          <t>Cat code</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -2273,7 +2410,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -2283,10 +2420,15 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Occurred</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+          <t>From</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
@@ -2298,6 +2440,11 @@
           <t>Header_1</t>
         </is>
       </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Event ID</t>
+        </is>
+      </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Year</t>
@@ -2318,7 +2465,12 @@
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
@@ -2327,12 +2479,12 @@
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CL-2100</t>
+          <t>EV-201</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2341,10 +2493,13 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>5400</v>
+        <v>1400</v>
       </c>
       <c r="F12" s="21" t="n">
         <v>44610</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>44611</v>
       </c>
       <c r="J12" s="18">
         <f>ROW()</f>
@@ -2354,24 +2509,27 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CL-2101</t>
+          <t>EV-201</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Windstorm Bettina</t>
+          <t>Windstorm Eunice</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>7600</v>
+        <v>4000</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>45688</v>
+        <v>44610</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>44611</v>
       </c>
       <c r="J13" s="18">
         <f>ROW()</f>
@@ -2381,7 +2539,7 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CL-2102</t>
+          <t>EV-202</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -2391,14 +2549,17 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Windstorm Kyrill II</t>
+          <t>Windstorm Bettina</t>
         </is>
       </c>
       <c r="E14" s="17" t="n">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>45635</v>
+        <v>45656</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>45659</v>
       </c>
       <c r="J14" s="18">
         <f>ROW()</f>
@@ -2406,16 +2567,76 @@
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="8" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>EV-202</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm Bettina</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>6600</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>45656</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>45659</v>
+      </c>
+      <c r="J15" s="18">
+        <f>ROW()</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>EV-203</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm Kyrill II</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>45635</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>45636</v>
+      </c>
+      <c r="J16" s="18">
+        <f>ROW()</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E15" s="19">
-        <f>SUM(E12:E14)</f>
-        <v>15400</v>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="E17" s="19">
+        <f>SUM(E12:E16)</f>
+        <v>14800</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>
@@ -4265,10 +4486,12 @@
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4328,10 +4551,17 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Occurrence year from = Event Date</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Claim no.</t>
+          <t>Cat code</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -4341,7 +4571,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -4351,10 +4581,20 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>Occurred</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+          <t>From</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>← source header, never read</t>
         </is>
@@ -4366,6 +4606,11 @@
           <t>Header_1</t>
         </is>
       </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Event ID</t>
+        </is>
+      </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Year</t>
@@ -4386,7 +4631,17 @@
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>← extraction row: blanks mean 'not extracted'</t>
         </is>
@@ -4395,12 +4650,12 @@
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CL-2100</t>
+          <t>EV-101</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -4409,10 +4664,16 @@
         </is>
       </c>
       <c r="E12" s="17" t="n">
-        <v>7200</v>
+        <v>400</v>
       </c>
       <c r="F12" s="21" t="n">
         <v>44963</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>44963</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>12</v>
       </c>
       <c r="J12" s="18">
         <f>ROW()</f>
@@ -4422,24 +4683,30 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CL-2101</t>
+          <t>EV-101</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Central Italy earthquake</t>
+          <t>Aegean earthquake M6.8</t>
         </is>
       </c>
       <c r="E13" s="17" t="n">
-        <v>950</v>
+        <v>6800</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>44519</v>
+        <v>44963</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>44963</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>188</v>
       </c>
       <c r="J13" s="18">
         <f>ROW()</f>
@@ -4447,16 +4714,53 @@
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="8" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>EV-102</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Central Italy earthquake</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>950</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>44519</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>44520</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="J14" s="18">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E14" s="19">
-        <f>SUM(E12:E13)</f>
+      <c r="E15" s="19">
+        <f>SUM(E12:E14)</f>
         <v>8150</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H15" s="19">
+        <f>SUM(H12:H14)</f>
+        <v>231</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>← selector empty: excluded from extraction, reused as control</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -143,6 +143,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -520,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V99"/>
+  <dimension ref="B1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1430,60 +1431,58 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="8" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Premium</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Incurred Losses</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -1495,7 +1494,7 @@
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -1507,31 +1506,31 @@
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1543,19 +1542,19 @@
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Sum Insured</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1567,7 +1566,7 @@
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1579,7 +1578,7 @@
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -1591,19 +1590,19 @@
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -1615,19 +1614,19 @@
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Date of Loss</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -1639,315 +1638,287 @@
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
+        <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="8" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Paid | Incurred</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Date format</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="3" t="inlineStr">
+    <row r="69">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="8" t="inlineStr">
+    <row r="70">
+      <c r="B70" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="10" t="n">
+    <row r="71">
+      <c r="B71" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="10" t="n">
+    <row r="72">
+      <c r="B72" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="10" t="n">
+    <row r="73">
+      <c r="B73" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="3" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D77" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G77" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I77" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G78" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -1955,9 +1926,9 @@
           <t>=</t>
         </is>
       </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
@@ -1975,33 +1946,33 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C80" s="11" t="inlineStr">
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>01.Premium@{N}</t>
+        </is>
+      </c>
+      <c r="D80" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
       <c r="F80" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
@@ -2015,33 +1986,33 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C81" s="11" t="inlineStr">
-        <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -2050,24 +2021,24 @@
       </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C82" s="11" t="inlineStr">
-        <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
@@ -2075,7 +2046,7 @@
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E82" s="11" t="inlineStr">
+      <c r="E82" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
@@ -2090,38 +2061,38 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>per risk</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
-        </is>
-      </c>
-      <c r="C83" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E83" s="11" t="inlineStr">
-        <is>
-          <t>03.Year basis</t>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -2130,22 +2101,22 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>cat losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>R-10</t>
-        </is>
-      </c>
-      <c r="C84" s="11" t="inlineStr">
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
@@ -2155,9 +2126,9 @@
           <t>=</t>
         </is>
       </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>04.Year basis</t>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
@@ -2170,139 +2141,179 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="3" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="8" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="12" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="13" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C90" s="4" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="12" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="13" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="12" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="13" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="12" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="13" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="12" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="13" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="12" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="13" t="inlineStr">
         <is>
           <t>Section_i = &lt;name&gt;</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>which section of the treaty block i belongs to</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="12" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="13" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="12" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="13" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="8" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2342,56 +2353,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
@@ -2435,37 +2446,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
@@ -2482,7 +2493,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -2492,16 +2503,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>1400</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <v>44610</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="22" t="n">
         <v>44611</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -2512,7 +2523,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -2522,16 +2533,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>4000</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="22" t="n">
         <v>44610</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="22" t="n">
         <v>44611</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -2542,7 +2553,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -2552,16 +2563,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>45656</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="22" t="n">
         <v>45659</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -2572,7 +2583,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -2582,16 +2593,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>6600</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="22" t="n">
         <v>45656</v>
       </c>
-      <c r="G15" s="21" t="n">
+      <c r="G15" s="22" t="n">
         <v>45659</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -2602,7 +2613,7 @@
           <t>EV-203</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -2612,16 +2623,16 @@
           <t>Windstorm Kyrill II</t>
         </is>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="18" t="n">
         <v>1800</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="22" t="n">
         <v>45635</v>
       </c>
-      <c r="G16" s="21" t="n">
+      <c r="G16" s="22" t="n">
         <v>45636</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -2632,7 +2643,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E17" s="19">
+      <c r="E17" s="20">
         <f>SUM(E12:E16)</f>
         <v>14800</v>
       </c>
@@ -2643,14 +2654,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2689,56 +2700,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -2772,22 +2783,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -2799,132 +2810,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>1240</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>15900</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>14930</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>1310</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>16740</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>10030</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>1395</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>17520</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>12660</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>1460</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>18390</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>11700</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1505</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>10250</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>1180</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>7100</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="19">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2934,15 +2945,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>SUM(C12:C17)</f>
         <v>8090</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>SUM(D12:D17)</f>
         <v>102150</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>SUM(G12:G17)</f>
         <v>66670</v>
       </c>
@@ -2985,56 +2996,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -3068,22 +3079,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -3095,132 +3106,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>860</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>6200</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>1200</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>890</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>6450</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>480</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>915</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>6700</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>8900</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>940</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>6980</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>620</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>960</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>7250</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>540</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>745</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>5430</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>410</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="19">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3230,15 +3241,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>SUM(C12:C17)</f>
         <v>5310</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>SUM(D12:D17)</f>
         <v>39010</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>SUM(G12:G17)</f>
         <v>12150</v>
       </c>
@@ -3281,56 +3292,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
@@ -3364,22 +3375,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -3391,132 +3402,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>1020</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <v>7400</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="18" t="n">
         <v>2300</v>
       </c>
-      <c r="L12" s="18">
+      <c r="L12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>1055</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <v>7690</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="18" t="n">
         <v>6800</v>
       </c>
-      <c r="L13" s="18">
+      <c r="L13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>1090</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <v>7980</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="18" t="n">
         <v>1450</v>
       </c>
-      <c r="L14" s="18">
+      <c r="L14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <v>1125</v>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <v>8300</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="18" t="n">
         <v>3200</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <v>1150</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <v>8600</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="18" t="n">
         <v>9100</v>
       </c>
-      <c r="L16" s="18">
+      <c r="L16" s="19">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n">
+      <c r="C17" s="18" t="n">
         <v>890</v>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <v>6440</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="18" t="n">
         <v>5300</v>
       </c>
-      <c r="L17" s="18">
+      <c r="L17" s="19">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3526,15 +3537,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>SUM(C12:C17)</f>
         <v>6330</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>SUM(D12:D17)</f>
         <v>46410</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>SUM(G12:G17)</f>
         <v>28150</v>
       </c>
@@ -3575,42 +3586,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -3639,17 +3650,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3661,75 +3672,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>18500</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="19">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>14400</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>19200</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>20900</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3739,7 +3750,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <f>SUM(C11:C14)</f>
         <v>73000</v>
       </c>
@@ -3750,7 +3761,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3787,42 +3798,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -3851,17 +3862,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -3873,75 +3884,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>7000</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="19">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>5430</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>7250</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>7900</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -3951,7 +3962,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <f>SUM(C11:C14)</f>
         <v>27580</v>
       </c>
@@ -3962,7 +3973,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3999,42 +4010,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
@@ -4063,17 +4074,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -4085,75 +4096,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="C11" s="18" t="n">
         <v>8300</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="18">
+      <c r="K11" s="19">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="C12" s="18" t="n">
         <v>6440</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="18">
+      <c r="K12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="C13" s="18" t="n">
         <v>8600</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="18">
+      <c r="K13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <v>9250</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="18">
+      <c r="K14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -4163,7 +4174,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <f>SUM(C11:C14)</f>
         <v>32590</v>
       </c>
@@ -4174,7 +4185,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4212,56 +4223,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
@@ -4300,27 +4311,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Name of Loss</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Date of Loss</t>
         </is>
@@ -4337,7 +4348,7 @@
           <t>CL-2100</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4347,13 +4358,13 @@
           <t>Warehouse fire, Lyon</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>1850</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <v>44269</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -4364,7 +4375,7 @@
           <t>CL-2101</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -4374,13 +4385,13 @@
           <t>Factory fire, Rotterdam</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>3400</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="22" t="n">
         <v>44953</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -4391,7 +4402,7 @@
           <t>CL-2102</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -4401,13 +4412,13 @@
           <t>Chemical plant fire, Basel</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>2600</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>45431</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -4418,7 +4429,7 @@
           <t>CL-2103</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -4428,13 +4439,13 @@
           <t>Cold store collapse, Milan</t>
         </is>
       </c>
-      <c r="E15" s="17" t="n">
+      <c r="E15" s="18" t="n">
         <v>1420</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="22" t="n">
         <v>45699</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="19">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -4445,7 +4456,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>SUM(E12:E15)</f>
         <v>9270</v>
       </c>
@@ -4456,14 +4467,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4503,56 +4514,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
@@ -4601,42 +4612,42 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>Number of Claims</t>
         </is>
@@ -4653,7 +4664,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -4663,19 +4674,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="18" t="n">
         <v>400</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="G12" s="21" t="n">
+      <c r="G12" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="19">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -4686,7 +4697,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -4696,19 +4707,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="18" t="n">
         <v>6800</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="G13" s="21" t="n">
+      <c r="G13" s="22" t="n">
         <v>44963</v>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <v>188</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="19">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -4719,7 +4730,7 @@
           <t>EV-102</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -4729,19 +4740,19 @@
           <t>Central Italy earthquake</t>
         </is>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="18" t="n">
         <v>950</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>44519</v>
       </c>
-      <c r="G14" s="21" t="n">
+      <c r="G14" s="22" t="n">
         <v>44520</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="18" t="n">
         <v>31</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="19">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -4752,11 +4763,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="20">
         <f>SUM(E12:E14)</f>
         <v>8150</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <f>SUM(H12:H14)</f>
         <v>231</v>
       </c>
@@ -4767,14 +4778,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V100"/>
+  <dimension ref="B1:V101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2279,41 +2279,53 @@
     <row r="96">
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Section_i = &lt;name&gt;</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which section of the treaty block i belongs to</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="13" t="inlineStr">
         <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="8" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V101"/>
+  <dimension ref="B1:V103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -565,7 +565,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Greyed rows are provisional sketches, not yet specified.</t>
+          <t>Greyed rows are declared but not yet implemented end to end.</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,27 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Sum Insured</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Premium</t>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
@@ -1530,7 +1540,7 @@
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band from</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1542,7 +1552,7 @@
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured</t>
+          <t>Band to</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -1554,31 +1564,31 @@
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -1590,7 +1600,7 @@
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -1602,408 +1612,352 @@
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
+        <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="B53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="3" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Paid | Incurred</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="3" t="inlineStr">
+    <row r="71">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="8" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="3" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G78" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H78" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I78" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C79" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E79" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C80" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E80" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E80" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G80" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>02.EPI@{N} re-est</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -2012,7 +1966,7 @@
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
@@ -2026,29 +1980,29 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
@@ -2061,38 +2015,38 @@
       </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -2101,38 +2055,38 @@
       </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
@@ -2146,186 +2100,266 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="8" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="8" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr">
+      <c r="C87" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H87" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="3" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="B90" s="8" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C92" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="8" t="inlineStr">
+    <row r="103">
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V103"/>
+  <dimension ref="B1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Band from</t>
+          <t>Band from (optional)</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Band to</t>
+          <t>Band to (optional)</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -1297,10 +1297,25 @@
       </c>
       <c r="Q14" s="7" t="inlineStr">
         <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
@@ -1782,262 +1797,206 @@
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Includes fac</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>yes | no</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Layered business</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>included | excluded</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
         <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="B71" s="3" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="B72" s="8" t="inlineStr">
+    <row r="74">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Suffix</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>9 months</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>est</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>9 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="2" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="3" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="8" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C80" s="8" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D80" s="8" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C81" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E81" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E82" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>02.EPI@{N} re-est</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
@@ -2046,7 +2005,7 @@
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
@@ -2060,29 +2019,29 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
@@ -2095,38 +2054,38 @@
       </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
@@ -2135,38 +2094,38 @@
       </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
@@ -2180,186 +2139,266 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="8" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D88" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="8" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C87" s="12" t="inlineStr">
+      <c r="C89" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D89" s="8" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E87" s="12" t="inlineStr">
+      <c r="E89" s="12" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="3" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="B92" s="8" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C94" s="8" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C94" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" s="8" t="inlineStr">
+    <row r="105">
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -17,6 +17,9 @@
     <sheet name="03. Large Losses Fire" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="04. Cat Losses EQ" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="04. Cat Losses Wind" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="05. Risk Profiles Fire" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="05. Risk Profiles EQ" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="05. Risk Profiles Wind" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,12 +60,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00999999"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Consolas"/>
       <sz val="9"/>
     </font>
@@ -75,6 +72,12 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="007F6000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -140,15 +143,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -521,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V105"/>
+  <dimension ref="B1:V107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1240,298 +1243,438 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>05. Risk Profiles</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>05 Profile</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles Fire</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>05 Profile Fire</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Band from (optional)</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Band to (optional)</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
       </c>
-      <c r="N14" s="7" t="inlineStr">
+      <c r="N14" s="6" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="O14" s="7" t="inlineStr">
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>Scale</t>
         </is>
       </c>
-      <c r="Q14" s="7" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>Share basis</t>
         </is>
       </c>
-      <c r="R14" s="7" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>Exposure basis</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="6" t="inlineStr">
         <is>
           <t>Includes fac</t>
         </is>
       </c>
-      <c r="T14" s="7" t="inlineStr">
+      <c r="T14" s="6" t="inlineStr">
         <is>
           <t>Layered business</t>
         </is>
       </c>
-      <c r="U14" s="7" t="inlineStr">
+      <c r="U14" s="6" t="inlineStr">
         <is>
           <t>As at</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles EQ</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>05 Profile EQ</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Band from (optional)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Band to (optional)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="U15" s="6" t="inlineStr">
+        <is>
+          <t>As at</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles Wind</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>05 Profile Wind</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Band from (optional)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Band to (optional)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="U16" s="6" t="inlineStr">
+        <is>
+          <t>As at</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="8" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Datasets</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>01, 02, 03</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>Earthquake</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>01, 02, 04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>Fire</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 03, 05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Earthquake</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
           <t>Windstorm</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>01, 02, 04</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 05</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="8" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Treaty type</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Fire + Nat Cat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Example Insurance SA</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
+          <t>Treaty type</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Fire + Nat Cat</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
           <t>Loss share warning</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C32" s="9" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="3" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="8" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Incurred Losses</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>EPI</t>
+          <t>Premium</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -1543,19 +1686,19 @@
     <row r="40">
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Incurred Losses</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Band from</t>
+          <t>EPI</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -1567,19 +1710,19 @@
     <row r="42">
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Band to</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Number of Risks</t>
+          <t>Band from</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -1591,7 +1734,7 @@
     <row r="44">
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Exposure</t>
+          <t>Band to</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -1603,31 +1746,31 @@
     <row r="45">
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
+          <t>Number of Risks</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
+          <t>Exposure</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
+          <t>Claim Reference</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -1639,7 +1782,7 @@
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Event Name</t>
+          <t>Name of Loss</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -1651,477 +1794,421 @@
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Loss amount</t>
+          <t>Event ID</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Number of Claims</t>
+          <t>Event Name</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Date of Loss</t>
+          <t>Loss amount</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Number of Claims</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="4" t="inlineStr">
         <is>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="4" t="inlineStr">
+        <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>A field name carries one type across the whole workbook.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="B57" s="3" t="inlineStr">
+    <row r="59">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>⟦VOCABULARY⟧</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="8" t="inlineStr">
+    <row r="60">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>Permitted values</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
+          <t>Year basis</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Paid | Incurred</t>
+          <t>UW | Occurrence</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
+          <t>Premium basis</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
+          <t>Loss basis</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Paid | Incurred</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
+          <t>PF transfer</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>yes | no</t>
+          <t>with clean cut | without clean cut | none</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Layered business</t>
+          <t>Exposure basis</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>included | excluded</t>
+          <t>Sum Insured | EML | PML | MPL</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Includes fac</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>yes | no</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
+          <t>Layered business</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>100% | ceded only</t>
+          <t>included | excluded</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>1 | 1,000 | 1,000,000</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
+          <t>Share basis</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Event Date | Event End Date</t>
+          <t>100% | ceded only</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="4" t="inlineStr">
         <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="3" t="inlineStr">
+    <row r="75">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="8" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="11" t="n">
+    <row r="77">
+      <c r="B77" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="11" t="n">
+    <row r="78">
+      <c r="B78" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="11" t="n">
+    <row r="79">
+      <c r="B79" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="3" t="inlineStr">
+    <row r="83">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="B82" s="8" t="inlineStr">
+    <row r="84">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D84" s="7" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H84" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="I84" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="8" t="inlineStr">
+    <row r="85">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="E85" s="11" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F85" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G83" s="4" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H83" s="5" t="inlineStr">
+      <c r="H85" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="8" t="inlineStr">
+    <row r="86">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C84" s="12" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>01.Premium@{N}</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E86" s="11" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>R-07</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>&gt;=</t>
-        </is>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="8" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>SUM(03.Loss amount@{Y})</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="E86" s="12" t="inlineStr">
-        <is>
-          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
@@ -2134,271 +2221,351 @@
       </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>a full-year N in History is an estimate, not an actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>R-07</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} re-est</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>02.EPI@{N} 9 months</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>R-01</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>SUM(03.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="8" t="inlineStr">
+    <row r="89">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C87" s="12" t="inlineStr">
+      <c r="C89" s="11" t="inlineStr">
         <is>
           <t>SUM(04.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D89" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E87" s="12" t="inlineStr">
+      <c r="E89" s="11" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F89" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>cat losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="8" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>R-09</t>
         </is>
       </c>
-      <c r="C88" s="12" t="inlineStr">
+      <c r="C90" s="11" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D90" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E88" s="12" t="inlineStr">
+      <c r="E90" s="11" t="inlineStr">
         <is>
           <t>03.Year basis</t>
         </is>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F90" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>history and large losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="8" t="inlineStr">
+    <row r="91">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C89" s="12" t="inlineStr">
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D91" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E89" s="12" t="inlineStr">
+      <c r="E91" s="11" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F91" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="G91" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H91" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="B91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="B93" s="3" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="8" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="13" t="inlineStr">
+    <row r="97">
+      <c r="B97" s="12" t="inlineStr">
         <is>
           <t>Header_i</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="13" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="12" t="inlineStr">
         <is>
           <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="B97" s="13" t="inlineStr">
+    <row r="99">
+      <c r="B99" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="13" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="12" t="inlineStr">
         <is>
           <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="B99" s="13" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="12" t="inlineStr">
         <is>
           <t>Transpose_i</t>
         </is>
       </c>
-      <c r="C99" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>block i is transposed</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="13" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="12" t="inlineStr">
         <is>
           <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
-      <c r="C100" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="B101" s="13" t="inlineStr">
+    <row r="103">
+      <c r="B103" s="12" t="inlineStr">
         <is>
           <t>Section_i = &lt;name&gt;</t>
         </is>
       </c>
-      <c r="C101" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>which section of the treaty block i belongs to</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="B102" s="13" t="inlineStr">
+    <row r="104">
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>&lt;Attribute&gt; = &lt;value&gt;</t>
         </is>
       </c>
-      <c r="C102" s="4" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="B103" s="13" t="inlineStr">
+    <row r="105">
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="B105" s="8" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2438,88 +2605,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>To</t>
         </is>
@@ -2723,7 +2890,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -2746,9 +2913,968 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles — Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Exposure basis = Sum Insured</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Includes fac = yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Layered business = excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>— Fire —</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Section_1 = Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>As at_1 = 30.09.2025</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Sum insured</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>0 – 1 000</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>620</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>310000</v>
+      </c>
+      <c r="J12" s="19">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>1 001 – 5 000</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>4900</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>480</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="J13" s="19">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>5 001 – 10 000</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>5001</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>5300</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>260</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>1880000</v>
+      </c>
+      <c r="J14" s="19">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>10 001 – 25 000</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>118</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>2010000</v>
+      </c>
+      <c r="J15" s="19">
+        <f>ROW()</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 25 000</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>27</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>1140000</v>
+      </c>
+      <c r="J16" s="19">
+        <f>ROW()</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E17" s="20">
+        <f>SUM(E12:E16)</f>
+        <v>20150</v>
+      </c>
+      <c r="F17" s="20">
+        <f>SUM(F12:F16)</f>
+        <v>1505</v>
+      </c>
+      <c r="G17" s="20">
+        <f>SUM(G12:G16)</f>
+        <v>6630000</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>Info_1 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>One profile per line of business. The top band is open at the top, so its upper bound is absent rather than zero.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles — Earthquake</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Exposure basis = Sum Insured</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Includes fac = yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Layered business = excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>— Earthquake —</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Section_1 = Earthquake</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>As at_1 = 30.09.2025</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Sum insured</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>0 – 2 500</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>380</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J12" s="19">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2 501 – 10 000</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>2300</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>310</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>690000</v>
+      </c>
+      <c r="J13" s="19">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>10 001 – 50 000</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>190</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>1420000</v>
+      </c>
+      <c r="J14" s="19">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 50 000</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>980000</v>
+      </c>
+      <c r="J15" s="19">
+        <f>ROW()</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E16" s="20">
+        <f>SUM(E12:E15)</f>
+        <v>7580</v>
+      </c>
+      <c r="F16" s="20">
+        <f>SUM(F12:F15)</f>
+        <v>960</v>
+      </c>
+      <c r="G16" s="20">
+        <f>SUM(G12:G15)</f>
+        <v>3330000</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Info_1 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>One profile per line of business. The top band is open at the top, so its upper bound is absent rather than zero.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>05. Risk Profiles — Windstorm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Currency = USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Scale = 1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Share basis = 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Exposure basis = Sum Insured</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Includes fac = yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Layered business = excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>— Windstorm —</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Section_1 = Windstorm</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>As at_1 = 30.09.2025</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Risks</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Sum insured</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>← source header, never read</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Header_1</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>← extraction row: blanks mean 'not extracted'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>0 – 2 500</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>450</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>290000</v>
+      </c>
+      <c r="J12" s="19">
+        <f>ROW()</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2 501 – 10 000</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>2650</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>370</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>810000</v>
+      </c>
+      <c r="J13" s="19">
+        <f>ROW()</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>10 001 – 50 000</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>10001</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>3180</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>240</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>1680000</v>
+      </c>
+      <c r="J14" s="19">
+        <f>ROW()</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>&gt; 50 000</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1910</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>90</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>1120000</v>
+      </c>
+      <c r="J15" s="19">
+        <f>ROW()</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E16" s="20">
+        <f>SUM(E12:E15)</f>
+        <v>9060</v>
+      </c>
+      <c r="F16" s="20">
+        <f>SUM(F12:F15)</f>
+        <v>1150</v>
+      </c>
+      <c r="G16" s="20">
+        <f>SUM(G12:G15)</f>
+        <v>3900000</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>← selector empty: excluded from extraction, reused as control</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Info_1 = J</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>One profile per line of business. The top band is open at the top, so its upper bound is absent rather than zero.</t>
         </is>
       </c>
     </row>
@@ -2785,78 +3911,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -3020,12 +4146,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3081,78 +4207,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -3316,12 +4442,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3377,78 +4503,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -3612,12 +4738,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3671,59 +4797,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -3830,7 +4956,7 @@
           <t>Info_1 = K</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -3846,7 +4972,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -3883,59 +5009,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -4042,7 +5168,7 @@
           <t>Info_1 = K</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -4058,7 +5184,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4095,59 +5221,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -4254,7 +5380,7 @@
           <t>Info_1 = K</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -4270,7 +5396,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4308,83 +5434,83 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Claim no.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Occurred</t>
         </is>
@@ -4536,7 +5662,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -4559,7 +5685,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4599,93 +5725,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>Claims</t>
         </is>
@@ -4843,7 +5969,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -4870,7 +5996,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Band (optional)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Band (optional)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Band</t>
+          <t>Band (optional)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,6 +144,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -524,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V107"/>
+  <dimension ref="B1:V124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1491,1081 +1492,1381 @@
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>⟦SECTIONS⟧</t>
+          <t>⟦INVENTORY⟧</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Section</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Kind</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Datasets</t>
+          <t>Holds</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>State</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>History</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 03, 05</t>
+          <t>Premium and loss history per section</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Earthquake</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>EPI Projections</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05</t>
+          <t>Estimated premium income, N and N+1</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Windstorm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Large Losses</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>01, 02, 04, 05</t>
+          <t>Individual large claims, per-risk sections</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Cat Losses</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Catastrophe events, cat sections</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Risk Profiles</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Banded exposure — the per-risk rating basis</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>EQ Aggs</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Earthquake sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>⟦GLOBAL⟧</t>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Wind Aggs</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Windstorm sums insured per cat zone</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Splits</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>axes settled, measures open</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Actual year</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>2025</v>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Rate Development</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Rate change history — optional</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Treaty type</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Fire + Nat Cat</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Triangles</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Loss development triangles</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Cedent</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Example Insurance SA</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Exchange rates</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>FX rates for conversion between currencies</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Loss share warning</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>0.2</v>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Collected step-2 blocks — written, never read</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>outstanding</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
+          <t>Every dataset the tool knows, whether or not this pack carries it. The register above lists what is here; ⟦SECTIONS⟧ says which roles each section expects, so a missing sheet reads as structure rather than as a gap.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>⟦TYPES⟧</t>
+          <t>⟦SECTIONS⟧</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>Datasets</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Year</t>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 03, 05</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Premium</t>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Earthquake</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 05</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Incurred Losses</t>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Windstorm</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>EPI</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>01, 02, 04, 05</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Band from</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>A section is a block. Per-risk sections carry large losses (03); cat sections carry event losses (04) instead. Rules are scoped by kind and evaluated once per applicable section, so an absent dataset is 'not applicable', not a gap.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Band to</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>⟦GLOBAL⟧</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Number of Risks</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
+          <t>Actual year</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Claim Reference</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Treaty type</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Fire + Nat Cat</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Name of Loss</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
+          <t>Cedent</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Example Insurance SA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Event ID</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
+          <t>Loss share warning</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Loss amount</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Number of Claims</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Actual year is N: the expiring year; the renewal is N+1. Sheet attributes override these; block attributes override the sheet. Loss share warning is the point above which a year's declared losses are flagged (§10.3).</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Date of Loss</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>⟦TYPES⟧</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Event Date</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>date</t>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Type</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Event End Date</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>A field name carries one type across the whole workbook.</t>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Incurred Losses</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>EPI</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>⟦VOCABULARY⟧</t>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Attribute</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Permitted values</t>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Band from</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Year basis</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>UW | Occurrence</t>
+          <t>Band to</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Premium basis</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>GWP | GNPI | Written | Earned | Signed</t>
+          <t>Number of Risks</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Loss basis</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Paid | Incurred</t>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>PF transfer</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>with clean cut | without clean cut | none</t>
+          <t>Claim Reference</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Exposure basis</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Sum Insured | EML | PML | MPL</t>
+          <t>Name of Loss</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Includes fac</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>yes | no</t>
+          <t>Event ID</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Layered business</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>included | excluded</t>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>1 | 1,000 | 1,000,000</t>
+          <t>Loss amount</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Share basis</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>100% | ceded only</t>
+          <t>Number of Claims</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Date format</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+          <t>Date of Loss</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Occurrence year from</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>Event Date | Event End Date</t>
+          <t>Event Date</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="4" t="inlineStr">
         <is>
+          <t>Event End Date</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>A field name carries one type across the whole workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>⟦VOCABULARY⟧</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>Permitted values</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Year basis</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>UW | Occurrence</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Premium basis</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>GWP | GNPI | Written | Earned | Signed</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Loss basis</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Paid | Incurred</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>PF transfer</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>with clean cut | without clean cut | none</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Exposure basis</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Sum Insured | EML | PML | MPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Includes fac</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>yes | no</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Layered business</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>included | excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>1 | 1,000 | 1,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Share basis</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>100% | ceded only</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Date format</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>ISO | DD.MM.YYYY | MM/DD/YYYY</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Occurrence year from</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Event Date | Event End Date</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="4" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>ISO 4217</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="B75" s="3" t="inlineStr">
+    <row r="92">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>⟦PERIOD ORDER⟧</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="7" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>Suffix</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="B77" s="10" t="n">
+    <row r="94">
+      <c r="B94" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="B78" s="10" t="n">
+    <row r="95">
+      <c r="B95" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>9 months</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="B79" s="10" t="n">
+    <row r="96">
+      <c r="B96" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>re-est</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="B81" s="2" t="inlineStr">
+    <row r="98">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="B83" s="3" t="inlineStr">
+    <row r="100">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="7" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C84" s="7" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="D84" s="7" t="inlineStr">
+      <c r="D101" s="7" t="inlineStr">
         <is>
           <t>Rel</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>Tolerance</t>
         </is>
       </c>
-      <c r="G84" s="7" t="inlineStr">
+      <c r="G101" s="7" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="H84" s="7" t="inlineStr">
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="B85" s="7" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>R-05</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C102" s="12" t="inlineStr">
         <is>
           <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
-      <c r="D85" s="7" t="inlineStr">
+      <c r="D102" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E85" s="11" t="inlineStr">
+      <c r="E102" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="F102" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G85" s="4" t="inlineStr">
+      <c r="G102" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H85" s="5" t="inlineStr">
+      <c r="H102" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="B86" s="7" t="inlineStr">
+    <row r="103">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>R-06</t>
         </is>
       </c>
-      <c r="C86" s="11" t="inlineStr">
+      <c r="C103" s="12" t="inlineStr">
         <is>
           <t>01.Premium@{N}</t>
         </is>
       </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="D103" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E86" s="11" t="inlineStr">
+      <c r="E103" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F103" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G86" s="4" t="inlineStr">
+      <c r="G103" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H103" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="7" t="inlineStr">
+    <row r="104">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>R-07</t>
         </is>
       </c>
-      <c r="C87" s="11" t="inlineStr">
+      <c r="C104" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} re-est</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D104" s="7" t="inlineStr">
         <is>
           <t>&gt;=</t>
         </is>
       </c>
-      <c r="E87" s="11" t="inlineStr">
+      <c r="E104" s="12" t="inlineStr">
         <is>
           <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F104" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G87" s="4" t="inlineStr">
+      <c r="G104" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H87" s="5" t="inlineStr">
+      <c r="H104" s="5" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="7" t="inlineStr">
+    <row r="105">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>R-01</t>
         </is>
       </c>
-      <c r="C88" s="11" t="inlineStr">
+      <c r="C105" s="12" t="inlineStr">
         <is>
           <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
+      <c r="D105" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E88" s="11" t="inlineStr">
+      <c r="E105" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F105" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G88" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H88" s="5" t="inlineStr">
+      <c r="H105" s="5" t="inlineStr">
         <is>
           <t>per risk</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="7" t="inlineStr">
+    <row r="106">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>R-02</t>
         </is>
       </c>
-      <c r="C89" s="11" t="inlineStr">
+      <c r="C106" s="12" t="inlineStr">
         <is>
           <t>SUM(04.Loss amount@{Y})</t>
         </is>
       </c>
-      <c r="D89" s="7" t="inlineStr">
+      <c r="D106" s="7" t="inlineStr">
         <is>
           <t>&lt;=</t>
         </is>
       </c>
-      <c r="E89" s="11" t="inlineStr">
+      <c r="E106" s="12" t="inlineStr">
         <is>
           <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F106" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G89" s="4" t="inlineStr">
+      <c r="G106" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="H106" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>cat losses cannot exceed total incurred for the same year</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>R-09</t>
-        </is>
-      </c>
-      <c r="C90" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
-        </is>
-      </c>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E90" s="11" t="inlineStr">
-        <is>
-          <t>03.Year basis</t>
-        </is>
-      </c>
-      <c r="F90" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>per risk</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>history and large losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>R-10</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>01.Year basis</t>
-        </is>
-      </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E91" s="11" t="inlineStr">
-        <is>
-          <t>04.Year basis</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>cat</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>history and cat losses must be on the same year basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Marker</t>
-        </is>
-      </c>
-      <c r="C96" s="7" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>Info_i = &lt;row&gt;</t>
-        </is>
-      </c>
-      <c r="C100" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="12" t="inlineStr">
-        <is>
-          <t>Transpose_i</t>
-        </is>
-      </c>
-      <c r="C101" s="4" t="inlineStr">
-        <is>
-          <t>block i is transposed</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>Dataset_i = &lt;key&gt;</t>
-        </is>
-      </c>
-      <c r="C102" s="4" t="inlineStr">
-        <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>Section_i = &lt;name&gt;</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr">
-        <is>
-          <t>which section of the treaty block i belongs to</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H107" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>R-10</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>04.Year basis</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>history and cat losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>Header_i</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>Header_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this column is block i's extraction column</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;col&gt;</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>Info_i = &lt;row&gt;</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>Transpose_i</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>block i is transposed</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>Dataset_i = &lt;key&gt;</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="13" t="inlineStr">
+        <is>
+          <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>the same, declared as a hypothesis — raises a query</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>
@@ -2605,88 +2906,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
@@ -2698,37 +2999,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
@@ -2745,7 +3046,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -2755,16 +3056,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>1400</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>44610</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="23" t="n">
         <v>44611</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -2775,7 +3076,7 @@
           <t>EV-201</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -2785,16 +3086,16 @@
           <t>Windstorm Eunice</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>4000</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>44610</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="23" t="n">
         <v>44611</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -2805,7 +3106,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -2815,16 +3116,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>45656</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>45659</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -2835,7 +3136,7 @@
           <t>EV-202</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -2845,16 +3146,16 @@
           <t>Windstorm Bettina</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>6600</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="23" t="n">
         <v>45656</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="23" t="n">
         <v>45659</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -2865,7 +3166,7 @@
           <t>EV-203</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -2875,16 +3176,16 @@
           <t>Windstorm Kyrill II</t>
         </is>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>1800</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <v>45635</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="23" t="n">
         <v>45636</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -2895,7 +3196,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <f>SUM(E12:E16)</f>
         <v>14800</v>
       </c>
@@ -2906,14 +3207,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -2952,42 +3253,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Exposure basis = Sum Insured</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Includes fac = yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Layered business = excluded</t>
         </is>
@@ -3001,44 +3302,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Fire</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>As at_1 = 30.09.2025</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Sum insured</t>
         </is>
@@ -3050,37 +3351,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Band from</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Band to</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
@@ -3097,22 +3398,22 @@
           <t>0 – 1 000</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>1000</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>2150</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>620</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>310000</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3123,22 +3424,22 @@
           <t>1 001 – 5 000</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1001</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>5000</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>4900</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>480</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>1290000</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3149,22 +3450,22 @@
           <t>5 001 – 10 000</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>5001</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>5300</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>260</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>1880000</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3175,22 +3476,22 @@
           <t>10 001 – 25 000</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>10001</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>25000</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>4700</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>118</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>2010000</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -3201,19 +3502,19 @@
           <t>&gt; 25 000</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>25000</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="19" t="n">
         <v>3100</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>1140000</v>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
@@ -3224,15 +3525,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <f>SUM(E12:E16)</f>
         <v>20150</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <f>SUM(F12:F16)</f>
         <v>1505</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="21">
         <f>SUM(G12:G16)</f>
         <v>6630000</v>
       </c>
@@ -3243,7 +3544,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
@@ -3289,42 +3590,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Exposure basis = Sum Insured</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Includes fac = yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Layered business = excluded</t>
         </is>
@@ -3338,44 +3639,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>As at_1 = 30.09.2025</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Sum insured</t>
         </is>
@@ -3387,37 +3688,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Band from</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Band to</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
@@ -3434,22 +3735,22 @@
           <t>0 – 2 500</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>2500</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>1050</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>380</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>240000</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3460,22 +3761,22 @@
           <t>2 501 – 10 000</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>2501</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>2300</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>310</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>690000</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3486,22 +3787,22 @@
           <t>10 001 – 50 000</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>10001</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>2750</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>190</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>1420000</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3512,19 +3813,19 @@
           <t>&gt; 50 000</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>1480</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>80</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>980000</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -3535,15 +3836,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>SUM(E12:E15)</f>
         <v>7580</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <f>SUM(F12:F15)</f>
         <v>960</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <f>SUM(G12:G15)</f>
         <v>3330000</v>
       </c>
@@ -3554,7 +3855,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
@@ -3600,42 +3901,42 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Exposure basis = Sum Insured</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Includes fac = yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Layered business = excluded</t>
         </is>
@@ -3649,44 +3950,44 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Section_1 = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>As at_1 = 30.09.2025</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Sum insured</t>
         </is>
@@ -3698,37 +3999,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Band</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Band from</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Band to</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Number of Risks</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Exposure</t>
         </is>
@@ -3745,22 +4046,22 @@
           <t>0 – 2 500</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>2500</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>1320</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="19" t="n">
         <v>450</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>290000</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -3771,22 +4072,22 @@
           <t>2 501 – 10 000</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>2501</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>10000</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>2650</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="19" t="n">
         <v>370</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>810000</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -3797,22 +4098,22 @@
           <t>10 001 – 50 000</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>10001</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>3180</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="19" t="n">
         <v>240</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>1680000</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -3823,19 +4124,19 @@
           <t>&gt; 50 000</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>1910</v>
       </c>
-      <c r="F15" s="18" t="n">
+      <c r="F15" s="19" t="n">
         <v>90</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>1120000</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -3846,15 +4147,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>SUM(E12:E15)</f>
         <v>9060</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="21">
         <f>SUM(F12:F15)</f>
         <v>1150</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="21">
         <f>SUM(G12:G15)</f>
         <v>3900000</v>
       </c>
@@ -3865,7 +4166,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
@@ -3911,78 +4212,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -3994,22 +4295,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -4021,132 +4322,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>1240</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>15900</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>14930</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1310</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>16740</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>10030</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>1395</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>17520</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>12660</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>1460</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>18390</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>11700</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>1505</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>19200</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>10250</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>1180</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>14400</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>7100</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4156,15 +4457,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C12:C17)</f>
         <v>8090</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>SUM(D12:D17)</f>
         <v>102150</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>SUM(G12:G17)</f>
         <v>66670</v>
       </c>
@@ -4207,78 +4508,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -4290,22 +4591,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -4317,132 +4618,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>860</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>6200</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>890</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>6450</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>480</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>915</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>6700</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>8900</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>940</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>6980</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>620</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>960</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>7250</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>540</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>745</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>5430</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>410</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4452,15 +4753,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C12:C17)</f>
         <v>5310</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>SUM(D12:D17)</f>
         <v>39010</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>SUM(G12:G17)</f>
         <v>12150</v>
       </c>
@@ -4503,78 +4804,78 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>H_PF transfer = with clean cut</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Policies</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Prem.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>Incurred</t>
         </is>
@@ -4586,22 +4887,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Incurred Losses</t>
         </is>
@@ -4613,132 +4914,132 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>1020</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="19" t="n">
         <v>7400</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="G12" s="19" t="n">
         <v>2300</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1055</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="19" t="n">
         <v>7690</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="19" t="n">
         <v>6800</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>1090</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>7980</v>
       </c>
-      <c r="G14" s="18" t="n">
+      <c r="G14" s="19" t="n">
         <v>1450</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>1125</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>8300</v>
       </c>
-      <c r="G15" s="18" t="n">
+      <c r="G15" s="19" t="n">
         <v>3200</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n">
+      <c r="C16" s="19" t="n">
         <v>1150</v>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="19" t="n">
         <v>8600</v>
       </c>
-      <c r="G16" s="18" t="n">
+      <c r="G16" s="19" t="n">
         <v>9100</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>ROW()</f>
         <v>16</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Info_1 = L</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
+      <c r="C17" s="19" t="n">
         <v>890</v>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="19" t="n">
         <v>6440</v>
       </c>
-      <c r="G17" s="18" t="n">
+      <c r="G17" s="19" t="n">
         <v>5300</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="20">
         <f>ROW()</f>
         <v>17</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -4748,15 +5049,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="21">
         <f>SUM(C12:C17)</f>
         <v>6330</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="21">
         <f>SUM(D12:D17)</f>
         <v>46410</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="21">
         <f>SUM(G12:G17)</f>
         <v>28150</v>
       </c>
@@ -4797,59 +5098,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -4861,17 +5162,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -4883,75 +5184,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>18500</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>14400</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>19200</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>20900</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -4961,7 +5262,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>SUM(C11:C14)</f>
         <v>73000</v>
       </c>
@@ -4972,7 +5273,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -5009,59 +5310,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -5073,17 +5374,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -5095,75 +5396,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>7000</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>5430</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>7250</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>7900</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -5173,7 +5474,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>SUM(C11:C14)</f>
         <v>27580</v>
       </c>
@@ -5184,7 +5485,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -5221,59 +5522,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Windstorm</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Premium basis = GNPI</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>EPI (net)</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Share %</t>
         </is>
@@ -5285,17 +5586,17 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
@@ -5307,75 +5608,75 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>2025 est</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>8300</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>ROW()</f>
         <v>11</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>2025 9 months</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>6440</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>2025 re-est</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>8600</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>9250</v>
       </c>
-      <c r="D14" s="21" t="n">
+      <c r="D14" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Info_1 = K</t>
         </is>
@@ -5385,7 +5686,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="21">
         <f>SUM(C11:C14)</f>
         <v>32590</v>
       </c>
@@ -5396,7 +5697,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -5434,83 +5735,83 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Fire</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Threshold = 500</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Claim no.</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>Occurred</t>
         </is>
@@ -5522,27 +5823,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Name of Loss</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Date of Loss</t>
         </is>
@@ -5559,7 +5860,7 @@
           <t>CL-2100</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -5569,13 +5870,13 @@
           <t>Warehouse fire, Lyon</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>1850</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>44269</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -5586,7 +5887,7 @@
           <t>CL-2101</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -5596,13 +5897,13 @@
           <t>Factory fire, Rotterdam</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>3400</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>44953</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -5613,7 +5914,7 @@
           <t>CL-2102</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -5623,13 +5924,13 @@
           <t>Chemical plant fire, Basel</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>2600</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>45431</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -5640,7 +5941,7 @@
           <t>CL-2103</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -5650,13 +5951,13 @@
           <t>Cold store collapse, Milan</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>1420</v>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="23" t="n">
         <v>45699</v>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="20">
         <f>ROW()</f>
         <v>15</v>
       </c>
@@ -5667,7 +5968,7 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="21">
         <f>SUM(E12:E15)</f>
         <v>9270</v>
       </c>
@@ -5678,14 +5979,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>
@@ -5725,93 +6026,93 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Section = Earthquake</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Currency = USD</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Scale = 1,000</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Share basis = 100%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>H_Year basis = UW</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>H_Loss basis = Incurred</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Date format = ISO</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Occurrence year from = Event Date</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Cat code</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>U/W Yr</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Event</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Gross incurred</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>Claims</t>
         </is>
@@ -5823,42 +6124,42 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Header_1</t>
         </is>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Event ID</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Event Name</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Loss amount</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Event Date</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="17" t="inlineStr">
         <is>
           <t>Event End Date</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Number of Claims</t>
         </is>
@@ -5875,7 +6176,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -5885,19 +6186,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="19" t="n">
         <v>400</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="H12" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>ROW()</f>
         <v>12</v>
       </c>
@@ -5908,7 +6209,7 @@
           <t>EV-101</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -5918,19 +6219,19 @@
           <t>Aegean earthquake M6.8</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="19" t="n">
         <v>6800</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="23" t="n">
         <v>44963</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="19" t="n">
         <v>188</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>ROW()</f>
         <v>13</v>
       </c>
@@ -5941,7 +6242,7 @@
           <t>EV-102</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
@@ -5951,19 +6252,19 @@
           <t>Central Italy earthquake</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>950</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>44519</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>44520</v>
       </c>
-      <c r="H14" s="18" t="n">
+      <c r="H14" s="19" t="n">
         <v>31</v>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="20">
         <f>ROW()</f>
         <v>14</v>
       </c>
@@ -5974,11 +6275,11 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="21">
         <f>SUM(E12:E14)</f>
         <v>8150</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="21">
         <f>SUM(H12:H14)</f>
         <v>231</v>
       </c>
@@ -5989,14 +6290,14 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Info_1 = J</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>As at = 31.12.2025</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -1685,12 +1685,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Occupancy x cover (Fire) or x Projects/Renewables (Eng.)</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>axes settled, measures open</t>
+          <t>The cedent's book split — sums insured, one block per section</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:V124"/>
+  <dimension ref="B1:V126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2395,156 +2395,96 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="B97" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>at inception</t>
+        </is>
+      </c>
+    </row>
     <row r="98">
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B98" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>at expiry</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Within one year the suffixes sort in this order, not alphabetically. A bare year sorts first; an unlisted suffix sorts last.</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" s="3" t="inlineStr">
+    <row r="102">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>⟦RULES⟧</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>Left</t>
-        </is>
-      </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Rel</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>Right</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>Tolerance</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>Severity</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>R-05</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} 9 months</t>
-        </is>
-      </c>
-      <c r="F102" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H102" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>R-06</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>01.Premium@{N}</t>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr">
+        <is>
+          <t>Left</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="inlineStr">
-        <is>
-          <t>02.EPI@{N} re-est</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>a full-year N in History is an estimate, not an actual</t>
+          <t>Rel</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>Right</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>Tolerance</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="I103" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>R-07</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>02.EPI@{N} re-est</t>
+          <t>01.Premium@{N} 9 months</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>&gt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E104" s="12" t="inlineStr">
@@ -2553,7 +2493,7 @@
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
@@ -2567,29 +2507,29 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
+          <t>same nine months reported in two sheets</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>R-01</t>
+          <t>R-06</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SUM(03.Loss amount@{Y})</t>
+          <t>01.Premium@{N}</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>=</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
@@ -2602,38 +2542,38 @@
       </c>
       <c r="H105" s="5" t="inlineStr">
         <is>
-          <t>per risk</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>large losses cannot exceed total incurred for the same year</t>
+          <t>a full-year N in History is an estimate, not an actual</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-07</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SUM(04.Loss amount@{Y})</t>
+          <t>02.EPI@{N} re-est</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>&lt;=</t>
+          <t>&gt;=</t>
         </is>
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>01.Incurred Losses@{Y}</t>
+          <t>02.EPI@{N} 9 months</t>
         </is>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
@@ -2642,38 +2582,38 @@
       </c>
       <c r="H106" s="5" t="inlineStr">
         <is>
-          <t>cat</t>
+          <t>all</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>cat losses cannot exceed total incurred for the same year</t>
+          <t>premium accrues; a re-estimate cannot fall below what is booked</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>R-09</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>01.Year basis</t>
+          <t>SUM(03.Loss amount@{Y})</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>=</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>03.Year basis</t>
+          <t>01.Incurred Losses@{Y}</t>
         </is>
       </c>
       <c r="F107" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
@@ -2687,186 +2627,266 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>history and large losses must be on the same year basis</t>
+          <t>large losses cannot exceed total incurred for the same year</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="7" t="inlineStr">
         <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>SUM(04.Loss amount@{Y})</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>01.Incurred Losses@{Y}</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H108" s="5" t="inlineStr">
+        <is>
+          <t>cat</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>cat losses cannot exceed total incurred for the same year</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>R-09</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>01.Year basis</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>03.Year basis</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>per risk</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>history and large losses must be on the same year basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="7" t="inlineStr">
+        <is>
           <t>R-10</t>
         </is>
       </c>
-      <c r="C108" s="12" t="inlineStr">
+      <c r="C110" s="12" t="inlineStr">
         <is>
           <t>01.Year basis</t>
         </is>
       </c>
-      <c r="D108" s="7" t="inlineStr">
+      <c r="D110" s="7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="E108" s="12" t="inlineStr">
+      <c r="E110" s="12" t="inlineStr">
         <is>
           <t>04.Year basis</t>
         </is>
       </c>
-      <c r="F108" s="4" t="n">
+      <c r="F110" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="4" t="inlineStr">
+      <c r="G110" s="4" t="inlineStr">
         <is>
           <t>error</t>
         </is>
       </c>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="H110" s="5" t="inlineStr">
         <is>
           <t>cat</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>history and cat losses must be on the same year basis</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="B110" s="2" t="inlineStr">
+    <row r="112">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Forms: &lt;key or role&gt;.&lt;field&gt;@&lt;record&gt; · &lt;key&gt;.&lt;attribute&gt; · SUM(&lt;key&gt;.&lt;field&gt;@&lt;record&gt;).  {N} resolves from ⟦GLOBAL⟧; {Y} expands once per year. Scope selects the sections a rule runs over.</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="B112" s="3" t="inlineStr">
+    <row r="114">
+      <c r="B114" s="3" t="inlineStr">
         <is>
           <t>⟦MARKERS⟧  —  written in column A of every other sheet</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="7" t="inlineStr">
+    <row r="115">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>Marker</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
         <is>
           <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="B114" s="13" t="inlineStr">
-        <is>
-          <t>Header_i</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>Header_i = &lt;col&gt;</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;col&gt;</t>
+          <t>Header_i</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>row-wise: this column holds the record selectors, =ROW()</t>
+          <t>row-wise: this row is block i's extraction row (declared labels only)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>Info_i = &lt;row&gt;</t>
+          <t>Header_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>transposed: this row holds the record selectors, =COLUMN()</t>
+          <t>transposed: this column is block i's extraction column</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>Transpose_i</t>
+          <t>Info_i = &lt;col&gt;</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>block i is transposed</t>
+          <t>row-wise: this column holds the record selectors, =ROW()</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>Dataset_i = &lt;key&gt;</t>
+          <t>Info_i = &lt;row&gt;</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>which dataset block i is — defaults to the sheet-name match</t>
+          <t>transposed: this row holds the record selectors, =COLUMN()</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>Section_i = &lt;name&gt;</t>
+          <t>Transpose_i</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>which section of the treaty block i belongs to</t>
+          <t>block i is transposed</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+          <t>Dataset_i = &lt;key&gt;</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+          <t>which dataset block i is — defaults to the sheet-name match</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="13" t="inlineStr">
         <is>
+          <t>Section_i = &lt;name&gt;</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>which section of the treaty block i belongs to</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>&lt;Attribute&gt; = &lt;value&gt;</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>an attribute of the sheet (unsuffixed) or block i (suffixed _i)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="13" t="inlineStr">
+        <is>
           <t>H_&lt;Attribute&gt; = &lt;val&gt;</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>the same, declared as a hypothesis — raises a query</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="B124" s="7" t="inlineStr">
+    <row r="126">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>No Header_i anywhere in column A  →  nothing is extracted from that sheet.</t>
         </is>

--- a/Intake_FireEQWind_v1.xlsx
+++ b/Intake_FireEQWind_v1.xlsx
@@ -1707,12 +1707,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Rate change history — optional</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>outstanding</t>
+          <t>The rate change a submission claims — the UW's own sheet</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>implemented</t>
         </is>
       </c>
     </row>
